--- a/artfynd/A 33883-2026 artfynd.xlsx
+++ b/artfynd/A 33883-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136042911</v>
       </c>
       <c r="B3" t="n">
-        <v>98210</v>
+        <v>98213</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 33883-2026 artfynd.xlsx
+++ b/artfynd/A 33883-2026 artfynd.xlsx
@@ -804,7 +804,7 @@
         <v>136042911</v>
       </c>
       <c r="B3" t="n">
-        <v>98213</v>
+        <v>98214</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
